--- a/consent_forms/025_waiver_submission_form--consent_forms.xlsx
+++ b/consent_forms/025_waiver_submission_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'acknowledge_risks_and_understand_the_activity_rules',_'value':_'i_acknowledge_and_understand_the_activity_rules,_including_the_risks_involved.'}</t>
+          <t>acknowledge_risks_and_understand_the_activity_rules</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Acknowledge risks and understand the activity rules', 'value': 'I acknowledge and understand the activity rules, including the risks involved.'}</t>
+          <t>Acknowledge risks and understand the activity rules</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'do_not_acknowledge_risks',_'value':_'i_do_not_acknowledge_and_accept_the_risks_involved'}</t>
+          <t>do_not_acknowledge_risks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Do not acknowledge risks', 'value': 'I do not acknowledge and accept the risks involved'}</t>
+          <t>Do not acknowledge risks</t>
         </is>
       </c>
     </row>
